--- a/artfynd/A 39629-2026 artfynd.xlsx
+++ b/artfynd/A 39629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137502215</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137502227</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137502240</v>
       </c>
       <c r="B4" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137502242</v>
       </c>
       <c r="B5" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137502269</v>
       </c>
       <c r="B6" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137502218</v>
       </c>
       <c r="B7" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137502259</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137502281</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137502235</v>
       </c>
       <c r="B10" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137502272</v>
       </c>
       <c r="B11" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137502276</v>
       </c>
       <c r="B12" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137502277</v>
       </c>
       <c r="B13" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137502282</v>
       </c>
       <c r="B14" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137502273</v>
       </c>
       <c r="B15" t="n">
-        <v>97544</v>
+        <v>97548</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>137502275</v>
       </c>
       <c r="B16" t="n">
-        <v>97544</v>
+        <v>97548</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>137502217</v>
       </c>
       <c r="B17" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>137502219</v>
       </c>
       <c r="B18" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>137502220</v>
       </c>
       <c r="B19" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>137502222</v>
       </c>
       <c r="B20" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>137502223</v>
       </c>
       <c r="B21" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>137502247</v>
       </c>
       <c r="B22" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>137502291</v>
       </c>
       <c r="B23" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137502221</v>
       </c>
       <c r="B24" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>137502213</v>
       </c>
       <c r="B25" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>137502225</v>
       </c>
       <c r="B26" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>137502250</v>
       </c>
       <c r="B27" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>137502212</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137502224</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>137502226</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>137502228</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137502232</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137502233</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137502234</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>137502236</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>137502241</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>137502246</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>137502251</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>137502253</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>137502254</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>137502260</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>137502263</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137502271</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>137502274</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>137502278</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>137502279</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>137502283</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>137502237</v>
       </c>
       <c r="B48" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>137502214</v>
       </c>
       <c r="B49" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>137502256</v>
       </c>
       <c r="B50" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>137502265</v>
       </c>
       <c r="B51" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>137502267</v>
       </c>
       <c r="B52" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>137502284</v>
       </c>
       <c r="B53" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>137502266</v>
       </c>
       <c r="B54" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>137502285</v>
       </c>
       <c r="B55" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137502239</v>
       </c>
       <c r="B56" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>137502216</v>
       </c>
       <c r="B57" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>137502292</v>
       </c>
       <c r="B58" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>137502231</v>
       </c>
       <c r="B59" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>137502238</v>
       </c>
       <c r="B60" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137502243</v>
       </c>
       <c r="B61" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>137502245</v>
       </c>
       <c r="B62" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>137502248</v>
       </c>
       <c r="B63" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>137502249</v>
       </c>
       <c r="B64" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>137502252</v>
       </c>
       <c r="B65" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>137502255</v>
       </c>
       <c r="B66" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>137502257</v>
       </c>
       <c r="B67" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>137502258</v>
       </c>
       <c r="B68" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>137502261</v>
       </c>
       <c r="B69" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>137502262</v>
       </c>
       <c r="B70" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>137502264</v>
       </c>
       <c r="B71" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>137502268</v>
       </c>
       <c r="B72" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>137502270</v>
       </c>
       <c r="B73" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>137502286</v>
       </c>
       <c r="B74" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>137502287</v>
       </c>
       <c r="B75" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>137502289</v>
       </c>
       <c r="B76" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>137502290</v>
       </c>
       <c r="B77" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>137502288</v>
       </c>
       <c r="B78" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
